--- a/Results/Phase 2/Methanol/methanol climate change results.xlsx
+++ b/Results/Phase 2/Methanol/methanol climate change results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4495471637953062</v>
+        <v>0.412530661142073</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4132599036727921</v>
+        <v>0.401509182094576</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4262659498643879</v>
+        <v>0.3961685110263413</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3357022418632702</v>
+        <v>0.3226401727296643</v>
       </c>
       <c r="F33" t="n">
-        <v>0.411788918636576</v>
+        <v>0.3874266068987406</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4822107603759224</v>
+        <v>0.4316875585613761</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4522616627285347</v>
+        <v>0.410350346124702</v>
       </c>
       <c r="I33" t="n">
-        <v>0.414549650016301</v>
+        <v>0.3891851817301812</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4522675830125251</v>
+        <v>0.4129398937825455</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4479244529303991</v>
+        <v>0.4089545504416087</v>
       </c>
       <c r="L33" t="n">
-        <v>0.49050543986725</v>
+        <v>0.4353605987569964</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5141020307151185</v>
+        <v>0.4468416812646754</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4552249828424526</v>
+        <v>0.4137263552999778</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7418401879135312</v>
+        <v>0.7099968603818508</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4354649272184781</v>
+        <v>0.4036075518897193</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4268913690171144</v>
+        <v>0.3968972982142589</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4164156144988059</v>
+        <v>0.3900760871722154</v>
       </c>
       <c r="S33" t="n">
-        <v>0.4616018054838313</v>
+        <v>0.4191365223435523</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4389592899241101</v>
+        <v>0.403477906521375</v>
       </c>
       <c r="U33" t="n">
-        <v>0.9070836735198228</v>
+        <v>0.8559903953274659</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4020388398650514</v>
+        <v>0.3833475311543846</v>
       </c>
       <c r="W33" t="n">
-        <v>0.8684401020224601</v>
+        <v>0.8240899667688205</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4386930795413894</v>
+        <v>0.4036660441797304</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4295141442708404</v>
+        <v>0.3988927731698504</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.6031905988287352</v>
+        <v>0.5737494949659241</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.458946770020156</v>
+        <v>0.4162037287289361</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.5114734379280255</v>
+        <v>0.4441759062493066</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3231330253809431</v>
+        <v>0.3255768025088604</v>
       </c>
       <c r="C33" t="n">
-        <v>0.347290244263694</v>
+        <v>0.350701987498454</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3333624881962606</v>
+        <v>0.3317980615017952</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2806276084885155</v>
+        <v>0.2815251308544194</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2929921151773237</v>
+        <v>0.3079596246896573</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3442802770254825</v>
+        <v>0.3386944373230693</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3428357369581835</v>
+        <v>0.3372268870201793</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3277906172979689</v>
+        <v>0.3285105584458533</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3353323123361699</v>
+        <v>0.3331338647146303</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3272753442331627</v>
+        <v>0.3280663461755576</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2642373680143533</v>
+        <v>0.2891473448506554</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3234886350929985</v>
+        <v>0.3259182775413159</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3260281832554594</v>
+        <v>0.3274946445105452</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5457408047358391</v>
+        <v>0.5544466153246588</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3233836398306767</v>
+        <v>0.3256944625892831</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3318429266335121</v>
+        <v>0.3309156771160466</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2269790598831377</v>
+        <v>0.2700812785663624</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3001307305481222</v>
+        <v>0.3112761610835985</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3092209928838762</v>
+        <v>0.3176743540516569</v>
       </c>
       <c r="U33" t="n">
-        <v>0.7434298058843469</v>
+        <v>0.7381619433421582</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3528622115006165</v>
+        <v>0.3439898934432217</v>
       </c>
       <c r="W33" t="n">
-        <v>0.7914313241502271</v>
+        <v>0.7570734722878434</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4474281986489465</v>
+        <v>0.4003195406361355</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3989380761139217</v>
+        <v>0.3705480564696099</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.4998100407489529</v>
+        <v>0.4932193119224197</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4250722257901175</v>
+        <v>0.3860902477628105</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.3347644477968718</v>
+        <v>0.3325626167998288</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4283313527929324</v>
+        <v>0.3984497143969685</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4039437330575211</v>
+        <v>0.3947480617165841</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4319584488251784</v>
+        <v>0.3981791261082896</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3329879635871364</v>
+        <v>0.320126710773322</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3969564040951528</v>
+        <v>0.3777721437002702</v>
       </c>
       <c r="G33" t="n">
-        <v>0.474437528582887</v>
+        <v>0.4260184537042577</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4280492938975564</v>
+        <v>0.3952305936896714</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3990329835728034</v>
+        <v>0.3788849427056233</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4453357313820738</v>
+        <v>0.4076156296857565</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4306465877656555</v>
+        <v>0.3987720220585005</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4743750798585571</v>
+        <v>0.4244971605261257</v>
       </c>
       <c r="M33" t="n">
-        <v>0.499149223237799</v>
+        <v>0.4370481503378431</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4366292636672375</v>
+        <v>0.4014970791519817</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7169731113822825</v>
+        <v>0.6904744315036569</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4413152261974631</v>
+        <v>0.4059959780054072</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4106270305050396</v>
+        <v>0.3861336413710298</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4142759834331959</v>
+        <v>0.3875223678984637</v>
       </c>
       <c r="S33" t="n">
-        <v>0.4526445550440376</v>
+        <v>0.4127117554075456</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4173353114859536</v>
+        <v>0.3896863559490823</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8810753337569663</v>
+        <v>0.8374622713449712</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3829154901190783</v>
+        <v>0.3706943610287674</v>
       </c>
       <c r="W33" t="n">
-        <v>0.866128802990749</v>
+        <v>0.8196143784780783</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4404582234374201</v>
+        <v>0.4035073112430522</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4219065933822236</v>
+        <v>0.3932808394473346</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.5822841647890594</v>
+        <v>0.5581061706552048</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4348047775088423</v>
+        <v>0.4008020296243853</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.5036699634481089</v>
+        <v>0.4383508673159247</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4105626927202486</v>
+        <v>0.3864506859311759</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4062037929910435</v>
+        <v>0.3949724286789356</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4392012904836524</v>
+        <v>0.4016492020801314</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3328095605779943</v>
+        <v>0.3193030833173631</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3837359238981834</v>
+        <v>0.3692485020057464</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4646260272183074</v>
+        <v>0.4195966392940605</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4154761941225812</v>
+        <v>0.3869625714989917</v>
       </c>
       <c r="I33" t="n">
-        <v>0.395152295790711</v>
+        <v>0.3757298217213847</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4378556903599112</v>
+        <v>0.4024036950406004</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4108796133836404</v>
+        <v>0.3866310231772405</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4549624654512031</v>
+        <v>0.4121515622017222</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4798531118473572</v>
+        <v>0.424850540465415</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4140882405251701</v>
+        <v>0.3872652666479696</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6909915024665508</v>
+        <v>0.6698404247944255</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4373586539952637</v>
+        <v>0.4029509073387541</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3794752574405681</v>
+        <v>0.3670100978907998</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4037523819494398</v>
+        <v>0.3805041699357632</v>
       </c>
       <c r="S33" t="n">
-        <v>0.4420937739600155</v>
+        <v>0.4056090610464175</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4074908220878291</v>
+        <v>0.3829836835145645</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8532760137698037</v>
+        <v>0.8180312413885964</v>
       </c>
       <c r="V33" t="n">
-        <v>0.39219277442548</v>
+        <v>0.3757122895609042</v>
       </c>
       <c r="W33" t="n">
-        <v>0.8484835368347968</v>
+        <v>0.8057300474367546</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4583946430698176</v>
+        <v>0.4132163784414566</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4442683903712564</v>
+        <v>0.4056397937069067</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.5772166160102093</v>
+        <v>0.554109753223702</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4293352419771345</v>
+        <v>0.3965915562947173</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4918562294209335</v>
+        <v>0.4305140709807196</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4013589231571662</v>
+        <v>0.3806675008009925</v>
       </c>
       <c r="C33" t="n">
-        <v>0.408671170451137</v>
+        <v>0.3955982575511682</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4101490310305891</v>
+        <v>0.3846574286727898</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3211401381112871</v>
+        <v>0.3120170231690877</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3880829154163013</v>
+        <v>0.3712859269702669</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4454040421045631</v>
+        <v>0.4080413923510965</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4071361250263441</v>
+        <v>0.3815474376904658</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3943928075717675</v>
+        <v>0.3748777494533397</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4276574441081791</v>
+        <v>0.3961004563542284</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4199621630971935</v>
+        <v>0.3916233864690374</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4359403084688089</v>
+        <v>0.4010105415282009</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4573019041442107</v>
+        <v>0.4122234391597939</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4043601106357142</v>
+        <v>0.3809213891766559</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6716244606703697</v>
+        <v>0.6546133691518041</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4293714799191676</v>
+        <v>0.3981520404627797</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3867479409101574</v>
+        <v>0.3709699286002369</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3966855834689393</v>
+        <v>0.3758347775942293</v>
       </c>
       <c r="S33" t="n">
-        <v>0.4310444252175865</v>
+        <v>0.3985857952316597</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4012525395711604</v>
+        <v>0.3787503345188593</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8545960365718406</v>
+        <v>0.8182203108573608</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4143338969748824</v>
+        <v>0.3891077741584152</v>
       </c>
       <c r="W33" t="n">
-        <v>0.8442529548894657</v>
+        <v>0.8015134388122143</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4597168378823919</v>
+        <v>0.4142024754627092</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4824198845868271</v>
+        <v>0.4271761087384734</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.5650382926863523</v>
+        <v>0.5456300374840602</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4325645497387415</v>
+        <v>0.3978257633686492</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4757695384249727</v>
+        <v>0.4211428199662621</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3449622027924929</v>
+        <v>0.3407009556130716</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3679104168390694</v>
+        <v>0.3651363647972285</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3619485087798195</v>
+        <v>0.3503442755133493</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2870848241955125</v>
+        <v>0.2870082626128484</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3346700045850559</v>
+        <v>0.3343476008901859</v>
       </c>
       <c r="G33" t="n">
-        <v>0.368670234106273</v>
+        <v>0.3557409324114154</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3481865962462038</v>
+        <v>0.3421211829093771</v>
       </c>
       <c r="I33" t="n">
-        <v>0.347667114419435</v>
+        <v>0.3419321255352089</v>
       </c>
       <c r="J33" t="n">
-        <v>0.359353014398837</v>
+        <v>0.3495228100342862</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3615013683265454</v>
+        <v>0.3506264321413537</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3398898981823945</v>
+        <v>0.3375495607924011</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3752324927336703</v>
+        <v>0.3588244653173217</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3518679737547749</v>
+        <v>0.3446243135285467</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5940508827768919</v>
+        <v>0.5913474803145549</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3453401584370902</v>
+        <v>0.3408969572001716</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3441588253263578</v>
+        <v>0.3400446262243082</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3009179264565403</v>
+        <v>0.3149213884155273</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3506944466068806</v>
+        <v>0.3445439472030198</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3426425896005163</v>
+        <v>0.3390748740497528</v>
       </c>
       <c r="U33" t="n">
-        <v>0.7911560724439065</v>
+        <v>0.7706198259400791</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3440824016687303</v>
+        <v>0.340164614492528</v>
       </c>
       <c r="W33" t="n">
-        <v>0.8127103814325067</v>
+        <v>0.7736468219136124</v>
       </c>
       <c r="X33" t="n">
-        <v>0.3803018237411944</v>
+        <v>0.3612404457011476</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3546291027556127</v>
+        <v>0.3462687061296212</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.4982401207135275</v>
+        <v>0.4938194226269995</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3846615968836211</v>
+        <v>0.3640718396657119</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.3731047539854346</v>
+        <v>0.356685025798998</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.302062729040608</v>
+        <v>0.3115805613246846</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3530864330233185</v>
+        <v>0.352781860873044</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3353273054178513</v>
+        <v>0.3318194634154821</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2332243631496958</v>
+        <v>0.251958555544633</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2880135655869963</v>
+        <v>0.3037004040352482</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3512873511798955</v>
+        <v>0.3422681362121087</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3297906629748132</v>
+        <v>0.3284572224949354</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3211248173180768</v>
+        <v>0.323374001420046</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3344335188953276</v>
+        <v>0.331507965293313</v>
       </c>
       <c r="K33" t="n">
-        <v>0.321554703200495</v>
+        <v>0.32343208993961</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2831782291202555</v>
+        <v>0.2982948639273144</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3254730373372084</v>
+        <v>0.3257915056072834</v>
       </c>
       <c r="N33" t="n">
-        <v>0.345119504806145</v>
+        <v>0.3377452106822045</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5658880806576488</v>
+        <v>0.5659865877016204</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3017903253659833</v>
+        <v>0.3113461644928527</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3294867806035071</v>
+        <v>0.3283523928302968</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2299552572010911</v>
+        <v>0.2701783460293417</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3160499933744245</v>
+        <v>0.3198289424042198</v>
       </c>
       <c r="T33" t="n">
-        <v>0.312321635427557</v>
+        <v>0.3179779686987</v>
       </c>
       <c r="U33" t="n">
-        <v>0.7247449041168071</v>
+        <v>0.7225156713393625</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3361045923715642</v>
+        <v>0.3325044938694148</v>
       </c>
       <c r="W33" t="n">
-        <v>0.7429465807593126</v>
+        <v>0.7239009718880079</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4311291368823261</v>
+        <v>0.3896145619041589</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3607428499758078</v>
+        <v>0.3468938539645262</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.4750040430406543</v>
+        <v>0.4737602600089167</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4050139932518779</v>
+        <v>0.3732195636172798</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.3272273265322963</v>
+        <v>0.3269578269027915</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2774002092991104</v>
+        <v>0.2952131857292164</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3326993040041087</v>
+        <v>0.3388226873925552</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3174697967170312</v>
+        <v>0.3199553202147138</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2253955423395702</v>
+        <v>0.2455388471854774</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2907952380107803</v>
+        <v>0.3043627859933273</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3435071596212357</v>
+        <v>0.3360252835517625</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3314831326805257</v>
+        <v>0.328195885081177</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3254663957668837</v>
+        <v>0.3247215206462238</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3270171721505907</v>
+        <v>0.3256851553443668</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3216310997735768</v>
+        <v>0.3223973998757548</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2682399882538167</v>
+        <v>0.2885612089698461</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3268267068063661</v>
+        <v>0.3255168712578311</v>
       </c>
       <c r="N33" t="n">
-        <v>0.346087585852744</v>
+        <v>0.3370345118648655</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5355274430187605</v>
+        <v>0.5423323095838439</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2918540610879676</v>
+        <v>0.3038717123514647</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3276521943388007</v>
+        <v>0.3260646197822549</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2290863179285066</v>
+        <v>0.2687228089570556</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3024043015656764</v>
+        <v>0.3104231020815715</v>
       </c>
       <c r="T33" t="n">
-        <v>0.314018395719144</v>
+        <v>0.3179403144685932</v>
       </c>
       <c r="U33" t="n">
-        <v>0.7167216701253691</v>
+        <v>0.7143585808001204</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3369674325137389</v>
+        <v>0.3318807653319915</v>
       </c>
       <c r="W33" t="n">
-        <v>0.7281300339804861</v>
+        <v>0.7111196127565089</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4597072343787894</v>
+        <v>0.4061399372075207</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.3481284144337062</v>
+        <v>0.3381320899939931</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.4498952553878825</v>
+        <v>0.4545256030627465</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4141196592737587</v>
+        <v>0.3773454520843875</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.3278778761285452</v>
+        <v>0.3261117045937391</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3911259700647574</v>
+        <v>0.3736256131336879</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3869976133387134</v>
+        <v>0.382404919653705</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4012652188774631</v>
+        <v>0.3780815014212796</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3121026811181575</v>
+        <v>0.3058449669575615</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3622329141288766</v>
+        <v>0.3553719798736675</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4596729008700196</v>
+        <v>0.4160962902671159</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4098151515680202</v>
+        <v>0.3825191625393334</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3682559992114571</v>
+        <v>0.3588556114435414</v>
       </c>
       <c r="J33" t="n">
-        <v>0.420824715022991</v>
+        <v>0.3914664290275745</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3892615797542712</v>
+        <v>0.3721297107813946</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4412945920091046</v>
+        <v>0.4034218970419149</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4761284404673261</v>
+        <v>0.4238566715304624</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4030443196329132</v>
+        <v>0.3795300868096939</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6685230763861159</v>
+        <v>0.6529438790882189</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4031764982689554</v>
+        <v>0.3807134496383956</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3760958942049035</v>
+        <v>0.3637717112835882</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3534414335924392</v>
+        <v>0.3502025190761358</v>
       </c>
       <c r="S33" t="n">
-        <v>0.402691356481651</v>
+        <v>0.3811070918356682</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3740771594392652</v>
+        <v>0.3622662634051573</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8474527818645159</v>
+        <v>0.8125257633276923</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3728225384703943</v>
+        <v>0.3624414352724122</v>
       </c>
       <c r="W33" t="n">
-        <v>0.8363174793689785</v>
+        <v>0.7965865457955686</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4248411359438244</v>
+        <v>0.392157189155791</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4136833717417873</v>
+        <v>0.3862724804969052</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.5470945916169708</v>
+        <v>0.5320216483095687</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.4214132367236852</v>
+        <v>0.3907048297079564</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.478467164687248</v>
+        <v>0.4217700855111353</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3295002390382419</v>
+        <v>0.3318567909022566</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3578458256758708</v>
+        <v>0.3600080247777221</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3457309960891251</v>
+        <v>0.3415700956908989</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2801103944759365</v>
+        <v>0.2833016629531951</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2968245431005171</v>
+        <v>0.312684343258657</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4288634779978797</v>
+        <v>0.3940721235336115</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3780865558183735</v>
+        <v>0.3599259292972353</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3269859041005183</v>
+        <v>0.3306058048315756</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3670682053263773</v>
+        <v>0.3551798350017525</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3371210184742365</v>
+        <v>0.3364146673836721</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2858396016237872</v>
+        <v>0.3047349780661109</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3367422574808636</v>
+        <v>0.3361866006921644</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3405748948020876</v>
+        <v>0.3385514657674384</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5748739255975147</v>
+        <v>0.5792823573964536</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3568971476619279</v>
+        <v>0.348682473375889</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3356737877498954</v>
+        <v>0.3355937615094956</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2515100982701</v>
+        <v>0.2870618571511343</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3066721239835348</v>
+        <v>0.3174751282424311</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3103085371787235</v>
+        <v>0.320789274771201</v>
       </c>
       <c r="U33" t="n">
-        <v>0.7550663539035752</v>
+        <v>0.7488374702475458</v>
       </c>
       <c r="V33" t="n">
-        <v>0.3531675075117915</v>
+        <v>0.3464790111182738</v>
       </c>
       <c r="W33" t="n">
-        <v>0.7815256659178451</v>
+        <v>0.7550163775444931</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4293212659515799</v>
+        <v>0.391300640919926</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.4567681318706696</v>
+        <v>0.4078350831851286</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.503396905905912</v>
+        <v>0.4980520452494728</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.3747359585205988</v>
+        <v>0.3588382475937418</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.4138858553212363</v>
+        <v>0.3808649254825413</v>
       </c>
     </row>
   </sheetData>
